--- a/diseases/d018/2015-2019.xlsx
+++ b/diseases/d018/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>13</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.02549823977314883</v>
       </c>
@@ -1801,9 +1798,6 @@
       <c r="O9" t="n">
         <v>7</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.01372982141631091</v>
       </c>
@@ -2689,9 +2683,6 @@
       <c r="O15" t="n">
         <v>14</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.02745964283262182</v>
       </c>
@@ -3577,9 +3568,6 @@
       <c r="O21" t="n">
         <v>10</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.01961403059472987</v>
       </c>
@@ -4613,9 +4601,6 @@
       <c r="O28" t="n">
         <v>25</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.04903507648682467</v>
       </c>
@@ -5501,9 +5486,6 @@
       <c r="O34" t="n">
         <v>19</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.03726665812998675</v>
       </c>
@@ -6389,9 +6371,6 @@
       <c r="O40" t="n">
         <v>20</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.03922806118945974</v>
       </c>
@@ -7425,9 +7404,6 @@
       <c r="O47" t="n">
         <v>22</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.04315086730840571</v>
       </c>
@@ -8313,9 +8289,6 @@
       <c r="O53" t="n">
         <v>19</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.03726665812998675</v>
       </c>
@@ -9201,9 +9174,6 @@
       <c r="O59" t="n">
         <v>76</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.149066632519947</v>
       </c>
@@ -10237,9 +10207,6 @@
       <c r="O66" t="n">
         <v>99</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.1941789028878257</v>
       </c>
@@ -11125,9 +11092,6 @@
       <c r="O72" t="n">
         <v>60</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.1176841835683792</v>
       </c>
@@ -12161,9 +12125,6 @@
       <c r="O79" t="n">
         <v>32</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.06238079541713248</v>
       </c>
@@ -13049,9 +13010,6 @@
       <c r="O85" t="n">
         <v>17</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.03313979756535163</v>
       </c>
@@ -13937,9 +13895,6 @@
       <c r="O91" t="n">
         <v>12</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.02339279828142468</v>
       </c>
@@ -14973,9 +14928,6 @@
       <c r="O98" t="n">
         <v>18</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.03508919742213702</v>
       </c>
@@ -15861,9 +15813,6 @@
       <c r="O104" t="n">
         <v>35</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.06822899498748865</v>
       </c>
@@ -16749,9 +16698,6 @@
       <c r="O110" t="n">
         <v>39</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.07602659441463021</v>
       </c>
@@ -17785,9 +17731,6 @@
       <c r="O117" t="n">
         <v>26</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.05068439627642014</v>
       </c>
@@ -18673,9 +18616,6 @@
       <c r="O123" t="n">
         <v>37</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.07212779470105943</v>
       </c>
@@ -19561,9 +19501,6 @@
       <c r="O129" t="n">
         <v>45</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.08772299355534256</v>
       </c>
@@ -20597,9 +20534,6 @@
       <c r="O136" t="n">
         <v>87</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.1695977875403289</v>
       </c>
@@ -21485,9 +21419,6 @@
       <c r="O142" t="n">
         <v>145</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.2826629792338816</v>
       </c>
@@ -22373,9 +22304,6 @@
       <c r="O148" t="n">
         <v>82</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.159850788256402</v>
       </c>
@@ -23409,9 +23337,6 @@
       <c r="O155" t="n">
         <v>39</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.07574834926138223</v>
       </c>
@@ -24297,9 +24222,6 @@
       <c r="O161" t="n">
         <v>14</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.02719171511947054</v>
       </c>
@@ -25185,9 +25107,6 @@
       <c r="O167" t="n">
         <v>19</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.03690304194785287</v>
       </c>
@@ -26221,9 +26140,6 @@
       <c r="O174" t="n">
         <v>28</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.05438343023894108</v>
       </c>
@@ -27109,9 +27025,6 @@
       <c r="O180" t="n">
         <v>28</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.05438343023894108</v>
       </c>
@@ -27997,9 +27910,6 @@
       <c r="O186" t="n">
         <v>40</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.07769061462705869</v>
       </c>
@@ -29033,9 +28943,6 @@
       <c r="O193" t="n">
         <v>34</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.06603702243299987</v>
       </c>
@@ -29921,9 +29828,6 @@
       <c r="O199" t="n">
         <v>40</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.07769061462705869</v>
       </c>
@@ -30957,9 +30861,6 @@
       <c r="O206" t="n">
         <v>41</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.07963287999273515</v>
       </c>
@@ -31845,9 +31746,6 @@
       <c r="O212" t="n">
         <v>91</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.1767461482765585</v>
       </c>
@@ -32733,9 +32631,6 @@
       <c r="O218" t="n">
         <v>105</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.203937863396029</v>
       </c>
@@ -33769,9 +33664,6 @@
       <c r="O225" t="n">
         <v>52</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.1009977990151763</v>
       </c>
@@ -34657,9 +34549,6 @@
       <c r="O231" t="n">
         <v>21</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.04066544626435011</v>
       </c>
@@ -35545,9 +35434,6 @@
       <c r="O237" t="n">
         <v>13</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.02517384768745483</v>
       </c>
@@ -36433,9 +36319,6 @@
       <c r="O243" t="n">
         <v>8</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.01549159857689528</v>
       </c>
@@ -37469,9 +37352,6 @@
       <c r="O250" t="n">
         <v>18</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.03485609679801438</v>
       </c>
@@ -38357,9 +38237,6 @@
       <c r="O256" t="n">
         <v>27</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.05228414519702157</v>
       </c>
@@ -39393,9 +39270,6 @@
       <c r="O263" t="n">
         <v>44</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.08520379217292404</v>
       </c>
@@ -40281,9 +40155,6 @@
       <c r="O269" t="n">
         <v>45</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.08714024199503595</v>
       </c>
@@ -41169,9 +41040,6 @@
       <c r="O275" t="n">
         <v>36</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.06971219359602876</v>
       </c>
@@ -42205,9 +42073,6 @@
       <c r="O282" t="n">
         <v>33</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.06390284412969303</v>
       </c>
@@ -43093,9 +42958,6 @@
       <c r="O288" t="n">
         <v>73</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.1413608370141694</v>
       </c>
@@ -43981,9 +43843,6 @@
       <c r="O294" t="n">
         <v>71</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.1374879373699456</v>
       </c>
@@ -45017,9 +44876,6 @@
       <c r="O301" t="n">
         <v>44</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.08520379217292404</v>
       </c>
@@ -45905,9 +45761,6 @@
       <c r="O307" t="n">
         <v>16</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0.03090721603522001</v>
       </c>
@@ -46941,9 +46794,6 @@
       <c r="O314" t="n">
         <v>16</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0.03090721603522001</v>
       </c>
@@ -47829,9 +47679,6 @@
       <c r="O320" t="n">
         <v>14</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.02704381403081751</v>
       </c>
@@ -48717,9 +48564,6 @@
       <c r="O326" t="n">
         <v>19</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.03670231904182376</v>
       </c>
@@ -49605,9 +49449,6 @@
       <c r="O332" t="n">
         <v>18</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0.03477061803962251</v>
       </c>
@@ -50641,9 +50482,6 @@
       <c r="O339" t="n">
         <v>31</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.05988273106823877</v>
       </c>
@@ -51529,9 +51367,6 @@
       <c r="O345" t="n">
         <v>31</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0.05988273106823877</v>
       </c>
@@ -52417,9 +52252,6 @@
       <c r="O351" t="n">
         <v>18</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0.03477061803962251</v>
       </c>
@@ -53453,9 +53285,6 @@
       <c r="O358" t="n">
         <v>34</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0.06567783407484251</v>
       </c>
@@ -54341,9 +54170,6 @@
       <c r="O364" t="n">
         <v>64</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0.12362886414088</v>
       </c>
@@ -55377,9 +55203,6 @@
       <c r="O371" t="n">
         <v>86</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0.1661262861893076</v>
       </c>
@@ -56264,9 +56087,6 @@
       </c>
       <c r="O377" t="n">
         <v>52</v>
-      </c>
-      <c r="Q377" t="n">
-        <v>0</v>
       </c>
       <c r="R377" t="n">
         <v>0.100448452114465</v>
